--- a/artfynd/A 14814-2024 artfynd.xlsx
+++ b/artfynd/A 14814-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117929467</v>
+        <v>117928869</v>
       </c>
       <c r="B2" t="n">
         <v>90782</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585761</v>
+        <v>585839</v>
       </c>
       <c r="R2" t="n">
-        <v>6980243</v>
+        <v>6980230</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117929411</v>
+        <v>117929784</v>
       </c>
       <c r="B3" t="n">
-        <v>103338</v>
+        <v>90782</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585800</v>
+        <v>585834</v>
       </c>
       <c r="R3" t="n">
-        <v>6980232</v>
+        <v>6980216</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117929784</v>
+        <v>117929411</v>
       </c>
       <c r="B4" t="n">
-        <v>90782</v>
+        <v>103338</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>222412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585834</v>
+        <v>585800</v>
       </c>
       <c r="R4" t="n">
-        <v>6980216</v>
+        <v>6980232</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117929216</v>
+        <v>117929530</v>
       </c>
       <c r="B5" t="n">
-        <v>100007</v>
+        <v>90782</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585787</v>
+        <v>585761</v>
       </c>
       <c r="R5" t="n">
-        <v>6980277</v>
+        <v>6980243</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117929159</v>
+        <v>117929216</v>
       </c>
       <c r="B6" t="n">
-        <v>90782</v>
+        <v>100007</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>222771</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585793</v>
+        <v>585787</v>
       </c>
       <c r="R6" t="n">
-        <v>6980241</v>
+        <v>6980277</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117928869</v>
+        <v>117929159</v>
       </c>
       <c r="B7" t="n">
         <v>90782</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585839</v>
+        <v>585793</v>
       </c>
       <c r="R7" t="n">
-        <v>6980230</v>
+        <v>6980241</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117936127</v>
+        <v>117936749</v>
       </c>
       <c r="B8" t="n">
         <v>90782</v>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585732</v>
+        <v>585845</v>
       </c>
       <c r="R8" t="n">
-        <v>6980110</v>
+        <v>6980250</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117936749</v>
+        <v>117936127</v>
       </c>
       <c r="B9" t="n">
         <v>90782</v>
@@ -1429,13 +1429,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585845</v>
+        <v>585732</v>
       </c>
       <c r="R9" t="n">
-        <v>6980250</v>
+        <v>6980110</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117935939</v>
+        <v>117935786</v>
       </c>
       <c r="B10" t="n">
         <v>90782</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585747</v>
+        <v>585760</v>
       </c>
       <c r="R10" t="n">
-        <v>6980187</v>
+        <v>6980242</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117935786</v>
+        <v>117935939</v>
       </c>
       <c r="B12" t="n">
         <v>90782</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585760</v>
+        <v>585747</v>
       </c>
       <c r="R12" t="n">
-        <v>6980242</v>
+        <v>6980187</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117936465</v>
+        <v>117936216</v>
       </c>
       <c r="B13" t="n">
         <v>90782</v>
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585799</v>
+        <v>585773</v>
       </c>
       <c r="R13" t="n">
-        <v>6980166</v>
+        <v>6980091</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117936216</v>
+        <v>117936465</v>
       </c>
       <c r="B14" t="n">
         <v>90782</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585773</v>
+        <v>585799</v>
       </c>
       <c r="R14" t="n">
-        <v>6980091</v>
+        <v>6980166</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 14814-2024 artfynd.xlsx
+++ b/artfynd/A 14814-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117928869</v>
+        <v>117929216</v>
       </c>
       <c r="B2" t="n">
-        <v>90782</v>
+        <v>100009</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>222771</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585839</v>
+        <v>585787</v>
       </c>
       <c r="R2" t="n">
-        <v>6980230</v>
+        <v>6980277</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117929784</v>
+        <v>117929159</v>
       </c>
       <c r="B3" t="n">
-        <v>90782</v>
+        <v>90784</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585834</v>
+        <v>585793</v>
       </c>
       <c r="R3" t="n">
-        <v>6980216</v>
+        <v>6980241</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -882,7 +882,7 @@
         <v>117929411</v>
       </c>
       <c r="B4" t="n">
-        <v>103338</v>
+        <v>103340</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117929530</v>
+        <v>117929784</v>
       </c>
       <c r="B5" t="n">
-        <v>90782</v>
+        <v>90784</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585761</v>
+        <v>585834</v>
       </c>
       <c r="R5" t="n">
-        <v>6980243</v>
+        <v>6980216</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117929216</v>
+        <v>117929467</v>
       </c>
       <c r="B6" t="n">
-        <v>100007</v>
+        <v>90784</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585787</v>
+        <v>585761</v>
       </c>
       <c r="R6" t="n">
-        <v>6980277</v>
+        <v>6980243</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117929159</v>
+        <v>117928869</v>
       </c>
       <c r="B7" t="n">
-        <v>90782</v>
+        <v>90784</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585793</v>
+        <v>585839</v>
       </c>
       <c r="R7" t="n">
-        <v>6980241</v>
+        <v>6980230</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117936749</v>
+        <v>117936127</v>
       </c>
       <c r="B8" t="n">
-        <v>90782</v>
+        <v>90784</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585845</v>
+        <v>585732</v>
       </c>
       <c r="R8" t="n">
-        <v>6980250</v>
+        <v>6980110</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117936127</v>
+        <v>117936082</v>
       </c>
       <c r="B9" t="n">
-        <v>90782</v>
+        <v>90784</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,13 +1429,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585732</v>
+        <v>585721</v>
       </c>
       <c r="R9" t="n">
-        <v>6980110</v>
+        <v>6980122</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1459,12 +1459,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117935786</v>
+        <v>117936216</v>
       </c>
       <c r="B10" t="n">
-        <v>90782</v>
+        <v>90784</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585760</v>
+        <v>585773</v>
       </c>
       <c r="R10" t="n">
-        <v>6980242</v>
+        <v>6980091</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117936082</v>
+        <v>117936749</v>
       </c>
       <c r="B11" t="n">
-        <v>90782</v>
+        <v>90784</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585721</v>
+        <v>585845</v>
       </c>
       <c r="R11" t="n">
-        <v>6980122</v>
+        <v>6980250</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117935939</v>
+        <v>117935786</v>
       </c>
       <c r="B12" t="n">
-        <v>90782</v>
+        <v>90784</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585747</v>
+        <v>585760</v>
       </c>
       <c r="R12" t="n">
-        <v>6980187</v>
+        <v>6980242</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117936216</v>
+        <v>117936465</v>
       </c>
       <c r="B13" t="n">
-        <v>90782</v>
+        <v>90784</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585773</v>
+        <v>585799</v>
       </c>
       <c r="R13" t="n">
-        <v>6980091</v>
+        <v>6980166</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117936465</v>
+        <v>117935939</v>
       </c>
       <c r="B14" t="n">
-        <v>90782</v>
+        <v>90784</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585799</v>
+        <v>585747</v>
       </c>
       <c r="R14" t="n">
-        <v>6980166</v>
+        <v>6980187</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 14814-2024 artfynd.xlsx
+++ b/artfynd/A 14814-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117929159</v>
+        <v>117928869</v>
       </c>
       <c r="B2" t="n">
-        <v>90786</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,25 +695,25 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarnbacken (Kvarnbacken), Jmt</t>
+          <t>Kvarnbacken, Kvarnbacken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585793</v>
+        <v>585839</v>
       </c>
       <c r="R2" t="n">
-        <v>6980241</v>
+        <v>6980230</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117928869</v>
+        <v>117929159</v>
       </c>
       <c r="B3" t="n">
-        <v>90786</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,25 +792,25 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvarnbacken (Kvarnbacken), Jmt</t>
+          <t>Kvarnbacken, Kvarnbacken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585839</v>
+        <v>585793</v>
       </c>
       <c r="R3" t="n">
-        <v>6980230</v>
+        <v>6980241</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,50 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117929216</v>
+        <v>117929467</v>
       </c>
       <c r="B4" t="n">
-        <v>100011</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kvarnbacken (Kvarnbacken), Jmt</t>
+          <t>Kvarnbacken, Kvarnbacken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585787</v>
+        <v>585761</v>
       </c>
       <c r="R4" t="n">
-        <v>6980277</v>
+        <v>6980243</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -984,12 +969,7 @@
         <v>117929784</v>
       </c>
       <c r="B5" t="n">
-        <v>90786</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,18 +986,18 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvarnbacken (Kvarnbacken), Jmt</t>
+          <t>Kvarnbacken, Kvarnbacken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117929467</v>
+        <v>117935786</v>
       </c>
       <c r="B6" t="n">
-        <v>90786</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,25 +1083,25 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kvarnbacken (Kvarnbacken), Jmt</t>
+          <t>Kvarnbacken, Kvarnbacken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585761</v>
+        <v>585760</v>
       </c>
       <c r="R6" t="n">
-        <v>6980243</v>
+        <v>6980242</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,50 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117929411</v>
+        <v>117935939</v>
       </c>
       <c r="B7" t="n">
-        <v>103343</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222412</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kvarnbacken (Kvarnbacken), Jmt</t>
+          <t>Kvarnbacken, Kvarnbacken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585800</v>
+        <v>585747</v>
       </c>
       <c r="R7" t="n">
-        <v>6980232</v>
+        <v>6980187</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117935939</v>
+        <v>117936082</v>
       </c>
       <c r="B8" t="n">
-        <v>90788</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,28 +1277,28 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kvarnbacken (Kvarnbacken), Jmt</t>
+          <t>Kvarnbacken, Kvarnbacken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585747</v>
+        <v>585721</v>
       </c>
       <c r="R8" t="n">
-        <v>6980187</v>
+        <v>6980122</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117936465</v>
+        <v>117936127</v>
       </c>
       <c r="B9" t="n">
-        <v>90788</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1414,25 +1374,25 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kvarnbacken (Kvarnbacken), Jmt</t>
+          <t>Kvarnbacken, Kvarnbacken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585799</v>
+        <v>585732</v>
       </c>
       <c r="R9" t="n">
-        <v>6980166</v>
+        <v>6980110</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117936749</v>
+        <v>117936216</v>
       </c>
       <c r="B10" t="n">
-        <v>90788</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,25 +1471,25 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kvarnbacken (Kvarnbacken), Jmt</t>
+          <t>Kvarnbacken, Kvarnbacken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585845</v>
+        <v>585773</v>
       </c>
       <c r="R10" t="n">
-        <v>6980250</v>
+        <v>6980091</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1593,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117935786</v>
+        <v>117936465</v>
       </c>
       <c r="B11" t="n">
-        <v>90788</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1618,25 +1568,25 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kvarnbacken (Kvarnbacken), Jmt</t>
+          <t>Kvarnbacken, Kvarnbacken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585760</v>
+        <v>585799</v>
       </c>
       <c r="R11" t="n">
-        <v>6980242</v>
+        <v>6980166</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1663,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117936127</v>
+        <v>117936749</v>
       </c>
       <c r="B12" t="n">
-        <v>90788</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1720,28 +1665,28 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kvarnbacken (Kvarnbacken), Jmt</t>
+          <t>Kvarnbacken, Kvarnbacken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585732</v>
+        <v>585845</v>
       </c>
       <c r="R12" t="n">
-        <v>6980110</v>
+        <v>6980250</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1797,53 +1742,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117936082</v>
+        <v>117929411</v>
       </c>
       <c r="B13" t="n">
-        <v>90788</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>222412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kvarnbacken (Kvarnbacken), Jmt</t>
+          <t>Kvarnbacken, Kvarnbacken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585721</v>
+        <v>585800</v>
       </c>
       <c r="R13" t="n">
-        <v>6980122</v>
+        <v>6980232</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1899,53 +1839,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117936216</v>
+        <v>117929216</v>
       </c>
       <c r="B14" t="n">
-        <v>90788</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>222771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kvarnbacken (Kvarnbacken), Jmt</t>
+          <t>Kvarnbacken, Kvarnbacken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585773</v>
+        <v>585787</v>
       </c>
       <c r="R14" t="n">
-        <v>6980091</v>
+        <v>6980277</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1969,12 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 14814-2024 artfynd.xlsx
+++ b/artfynd/A 14814-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117928869</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117929159</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117929467</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117929784</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117935786</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117935939</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117936082</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117936127</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117936216</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117936465</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117936749</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117929411</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,8 +1998,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117929216</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>